--- a/JsonConverter/ExcelFiles/Chapter.xlsx
+++ b/JsonConverter/ExcelFiles/Chapter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62976365-13CD-492E-B2DE-7565C10842F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8B1A8A-20AF-4BCC-A998-F4ADED6590E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7485" yWindow="1020" windowWidth="23820" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3225" yWindow="300" windowWidth="25095" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>Name</t>
   </si>
@@ -140,18 +140,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>자연의 역습</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>변이된 생물들이 도심까지 침투했다.\n군대도 막지 못한 괴물들이 거리를 점령했다.\n살아남은 자들은 지하로 숨어들었다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>오염된 자연이 스스로 진화하기 시작했다.\n식물과 동물의 경계가 사라진 듯한 생명체가 등장했다.\n지구는 더 이상 인간의 것이 아니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Map/Prefab/Chapter01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -187,7 +175,65 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>방사능 물질을 대기권에 퍼뜨리기 시작했다.\n돌연변이 생물들이 출몰하고 있다.\n인류의 저항이 시작된다.</t>
+    <t>Chapter_Earth_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류의 황혼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>방사능 물질을 대기권에 퍼뜨리기 시작했다.\n지구의 생태계가 서서히 무너지고 있다..\n지구 종말 프로젝트가 시작된다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오염된 도심에 발을 들였다.\n저항하는 자들을 하나씩 쓰러뜨린다.\n이 도시는 곧 나의 것이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>야생의 침묵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오염이 퍼지며 야생의 소리가 사라져간다.\n변이된 생물들조차 숨죽인 이 땅을 짓밟아라.\n침묵 속에서 침략은 계속된다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류의 마지막 저항선에 도달했다.\n이 전선을 무너뜨리면 지구는 내 것이 된다.\n종말의 완성까지 단 한 걸음 남았다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map/Thumbnail/Chapter04_Thumbnail</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ap/Prefab/Chapter04</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hapter04</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -858,13 +904,13 @@
         <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -878,13 +924,13 @@
         <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>15</v>
@@ -895,25 +941,40 @@
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>27</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>

--- a/JsonConverter/ExcelFiles/Chapter.xlsx
+++ b/JsonConverter/ExcelFiles/Chapter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8B1A8A-20AF-4BCC-A998-F4ADED6590E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66232C74-52BB-41CA-A779-B02A7F5BFE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="300" windowWidth="25095" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12570" yWindow="15" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
   <si>
     <t>Name</t>
   </si>
@@ -44,19 +44,19 @@
   </si>
   <si>
     <t>챕터 고유 Id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>챕터 설명(표기용)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>챕터 대표 이미지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>챕터 프리팹</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -88,11 +88,11 @@
       </rPr>
       <t>번호</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -107,11 +107,11 @@
       </rPr>
       <t>hapterNum</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chapter01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chapter02</t>
@@ -121,27 +121,23 @@
   </si>
   <si>
     <t>Chapter_Earth_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chapter_Earth_2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chapter_Earth_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>오염의 시작</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>도시의 붕괴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Map/Prefab/Chapter01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -156,55 +152,39 @@
       </rPr>
       <t>ap/Thumbnail/Chapter01_Thumbnail</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Map/Prefab/Chapter03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Map/Prefab/Chapter02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Map/Thumbnail/Chapter02_Thumbnail</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Map/Thumbnail/Chapter03_Thumbnail</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chapter_Earth_4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>인류의 황혼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>방사능 물질을 대기권에 퍼뜨리기 시작했다.\n지구의 생태계가 서서히 무너지고 있다..\n지구 종말 프로젝트가 시작된다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>오염된 도심에 발을 들였다.\n저항하는 자들을 하나씩 쓰러뜨린다.\n이 도시는 곧 나의 것이다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>야생의 침묵</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>오염이 퍼지며 야생의 소리가 사라져간다.\n변이된 생물들조차 숨죽인 이 땅을 짓밟아라.\n침묵 속에서 침략은 계속된다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>인류의 마지막 저항선에 도달했다.\n이 전선을 무너뜨리면 지구는 내 것이 된다.\n종말의 완성까지 단 한 걸음 남았다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Map/Thumbnail/Chapter04_Thumbnail</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -219,7 +199,7 @@
       </rPr>
       <t>ap/Prefab/Chapter04</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -234,18 +214,241 @@
       </rPr>
       <t>hapter04</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter_Earth_5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter_Earth_6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter_Earth_7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>종말의 시작</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>검은 침묵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>오염이 퍼지며 야생의 소리가 사라져간다.\n그 어떠한 생명체도 소리를 내지 않는다.\n침묵 속에서 종말은 계속된다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>붉은 계획</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>멸망 프로토콜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>외계의 유산</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최후의 저항</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류의 마지막 저항선에 도달했다.\n이 전선을 무너뜨리면 지구는 내 것이 된다.\n하지만 인류의 저항이 생각보다 거세다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구를 지키기 위한 비밀무기를 꺼냈다.\n상대하기 힘들어보일지도 모른다.\n잠깐.. 사람이..?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 분명 저 외계에서 태어났는데..\n앗 머리가…\n이상한 기억이 떠오르기 시작한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map/Thumbnail/Chapter05_Thumbnail</t>
+  </si>
+  <si>
+    <t>Map/Thumbnail/Chapter06_Thumbnail</t>
+  </si>
+  <si>
+    <t>Map/Thumbnail/Chapter07_Thumbnail</t>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ap/Prefab/Chapter05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ap/Prefab/Chapter06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ap/Prefab/Chapter07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hapter05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hapter06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hapter07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>저것은..!\n진실을 파헤치기 위해선 쓰러뜨리는 방법밖에 없다.\n이게 내 마지막 전투가 될 것이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -385,33 +588,33 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -901,16 +1104,16 @@
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -921,16 +1124,16 @@
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>15</v>
@@ -941,16 +1144,16 @@
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>16</v>
@@ -958,38 +1161,83 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="B9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
@@ -2082,7 +2330,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/Chapter.xlsx
+++ b/JsonConverter/ExcelFiles/Chapter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66232C74-52BB-41CA-A779-B02A7F5BFE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFEEC5A-4102-4EAD-9C0F-23C9A9621EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12570" yWindow="15" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="990" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -175,14 +175,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>방사능 물질을 대기권에 퍼뜨리기 시작했다.\n지구의 생태계가 서서히 무너지고 있다..\n지구 종말 프로젝트가 시작된다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>오염된 도심에 발을 들였다.\n저항하는 자들을 하나씩 쓰러뜨린다.\n이 도시는 곧 나의 것이다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Map/Thumbnail/Chapter04_Thumbnail</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -233,39 +225,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>검은 침묵</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>오염이 퍼지며 야생의 소리가 사라져간다.\n그 어떠한 생명체도 소리를 내지 않는다.\n침묵 속에서 종말은 계속된다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>붉은 계획</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>멸망 프로토콜</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>외계의 유산</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>최후의 저항</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>인류의 마지막 저항선에 도달했다.\n이 전선을 무너뜨리면 지구는 내 것이 된다.\n하지만 인류의 저항이 생각보다 거세다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>지구를 지키기 위한 비밀무기를 꺼냈다.\n상대하기 힘들어보일지도 모른다.\n잠깐.. 사람이..?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 분명 저 외계에서 태어났는데..\n앗 머리가…\n이상한 기억이 떠오르기 시작한다.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -429,6 +397,38 @@
   </si>
   <si>
     <t>저것은..!\n진실을 파헤치기 위해선 쓰러뜨리는 방법밖에 없다.\n이게 내 마지막 전투가 될 것이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구를 정복하기 위해 왔다.\n나약한 인류를 모조리 없애버리겠다.\n지금부터 지구 종말 프로젝트가 시작된다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>붕괴된 도시에 발을 들였다.\n저항하는 자들은 모조리 쓰러뜨린다.\n이 지구는 곧 나의 것이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼돈이 가득한 지구에서 군인들이 나서기 시작했다.\n인류의 힘은 고작 이것 뿐인가.\n지구는 서서히 죽어가기 시작한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project.이클립스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼돈의 서막</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류는 지구를 지키기 위해 비밀무기를 꺼냈다.\n상대하기 힘들어보일지도 모른다.\n잠깐.. 사람이..?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>외계종족이 나뿐만이 아니었다니...\n앗 머리가…\n이상한 기억이 떠오르기 시작한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류의 마지막 저항선에 도달했다.\n이 전선을 무너뜨려 쐐기를 박을때다.\n하지만 인류의 저항이 생각보다 거세다.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1104,10 +1104,10 @@
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>22</v>
@@ -1127,7 +1127,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>25</v>
@@ -1144,10 +1144,10 @@
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>26</v>
@@ -1164,79 +1164,79 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>48</v>
-      </c>
       <c r="E10" s="15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
